--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.30_Q100_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.30_Q100_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02789850740476674</v>
+        <v>0.01376033964634492</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02789850740476674</v>
+        <v>0.01376033964634492</v>
       </c>
       <c r="D2" t="n">
-        <v>0.006908093707673569</v>
+        <v>0.005979601454566303</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0747361165861344</v>
+        <v>0.03789669649881942</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0747361165861344</v>
+        <v>0.03789669649881942</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01711111691173477</v>
+        <v>0.01434610690899107</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1558249617011253</v>
+        <v>0.07856320644630639</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1558249617011253</v>
+        <v>0.07856320644630639</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009411091566614698</v>
+        <v>0.02441540223974717</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2128900108368141</v>
+        <v>0.1075060016705152</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2128900108368141</v>
+        <v>0.1075060016705152</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01643796673551175</v>
+        <v>0.03447599498544392</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2072405895329955</v>
+        <v>0.104454186833166</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2072405895329955</v>
+        <v>0.104454186833166</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01891005933274124</v>
+        <v>0.03233484666140389</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1874041487340025</v>
+        <v>0.09457129302013276</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1874041487340025</v>
+        <v>0.09457129302013276</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01890457176462514</v>
+        <v>0.02786988802273808</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.170027818738149</v>
+        <v>0.08592544506168945</v>
       </c>
       <c r="C8" t="n">
-        <v>0.170027818738149</v>
+        <v>0.08592544506168945</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0202589584121667</v>
+        <v>0.02497140774297437</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1594888699388254</v>
+        <v>0.08067544420159217</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1594888699388254</v>
+        <v>0.08067544420159217</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0225266999728954</v>
+        <v>0.02333869804070929</v>
       </c>
     </row>
   </sheetData>
